--- a/reports/pdf_weekly_20260821.xlsx
+++ b/reports/pdf_weekly_20260821.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +57,10 @@
     <font>
       <b val="1"/>
       <color rgb="000070C0"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
     <font>
       <b val="1"/>
@@ -128,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -167,7 +171,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -536,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>주간 변화  ·  2026-08-18 ~ 2026-08-21  (4거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>주간 변화  ·  2026-08-18 ~ 2026-08-21  (4거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,586억   ·   현금 275억(5.8%)      주말 2026-08-21  vs  주초 2026-08-18      매수 10종목  /  매도 11종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,586억   ·   현금 82억(1.7%)      주말 2026-08-21  vs  주초 2026-08-18      매수 13종목  /  매도 17종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -658,23 +663,23 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>감성코퍼레이션</t>
+          <t>코미코  (신규)</t>
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>113</v>
+        <v>420</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>455390000</v>
+        <v>9522240000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>0.43%→0.50%</t>
+          <t>0.00%→2.04%</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>440→553</t>
+          <t>0→420</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -683,19 +688,19 @@
         </is>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-189</v>
+        <v>-283</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1890907200</v>
+        <v>-2866676800</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>1.00%→0.59%</t>
+          <t>1.00%→0.37%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>452→263</t>
+          <t>452→169</t>
         </is>
       </c>
     </row>
@@ -706,151 +711,151 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>100</v>
+        <v>149</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>4752800000</v>
+        <v>7438080000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.06%</t>
+          <t>0.00%→1.59%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>0→100</t>
+          <t>0→149</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>저스템</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-79</v>
+        <v>-101</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-3007056000</v>
+        <v>-1340310400</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>1.63%→1.01%</t>
+          <t>0.77%→0.43%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>198→119</t>
+          <t>253→152</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>하림지주</t>
+          <t>감성코퍼레이션</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>477162400</v>
+        <v>461853600</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.61%→0.71%</t>
+          <t>0.43%→0.48%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>244→287</t>
+          <t>440→553</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>저스템</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-66</v>
+        <v>-93</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-885456000</v>
+        <v>-1343440800</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.77%→0.56%</t>
+          <t>0.94%→0.53%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>253→187</t>
+          <t>263→170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>큐리언트</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>441417600</v>
+        <v>1462968000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>1.05%→1.06%</t>
+          <t>1.27%→1.60%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>349→385</t>
+          <t>222→276</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-62</v>
+        <v>-79</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-925288000</v>
+        <v>-3031704000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.94%→0.67%</t>
+          <t>1.63%→0.98%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>263→201</t>
+          <t>198→119</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>큐리언트</t>
+          <t>하림지주</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>945360000</v>
+        <v>478951200</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>1.27%→1.52%</t>
+          <t>0.61%→0.68%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>222→258</t>
+          <t>244→287</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -859,42 +864,42 @@
         </is>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-25</v>
+        <v>-38</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-889200000</v>
+        <v>-1414816000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.64%→0.39%</t>
+          <t>0.64%→0.29%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>74→49</t>
+          <t>74→36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>970632000</v>
+        <v>449280000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.70%</t>
+          <t>1.05%→1.03%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>116→133</t>
+          <t>349→385</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -906,11 +911,11 @@
         <v>-24</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-954720000</v>
+        <v>-968448000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.81%→0.66%</t>
+          <t>0.81%→0.64%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
@@ -922,337 +927,392 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1583400000</v>
+        <v>885768000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.93%→1.18%</t>
+          <t>1.43%→1.48%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>35→50</t>
+          <t>116→133</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-13</v>
+        <v>-23</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-918008000</v>
+        <v>-464048000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>6.32%→6.08%</t>
+          <t>3.60%→3.30%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>398→385</t>
+          <t>787→764</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>473616000</v>
+        <v>1613040000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.89%→1.04%</t>
+          <t>0.93%→1.15%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>106→118</t>
+          <t>35→50</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-321152000</v>
+        <v>-939640000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.51%</t>
+          <t>6.32%→5.96%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>65→57</t>
+          <t>398→385</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>872872000</v>
+        <v>536536000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.77%→0.92%</t>
+          <t>0.33%→0.46%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>41→52</t>
+          <t>42→56</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-7</v>
+        <v>-12</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-939848000</v>
+        <v>-305760000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>2.29%→2.07%</t>
+          <t>0.17%→0.10%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>76→69</t>
+          <t>31→19</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
+          <t>티에프이</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>506688000</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>0.89%→1.07%</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>106→118</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>-470496000</v>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>1.48%→1.35%</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>173→161</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>두산테스나</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>939224000</v>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>0.77%→0.95%</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>41→52</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>씨메스로보틱스</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>-226283200</v>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>0.31%→0.23%</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>64→53</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>1038024000</v>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>1.19%→1.46%</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>50→59</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>솔브레인홀딩스</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>-324480000</v>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>0.58%→0.50%</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>65→57</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" s="11" t="n">
-        <v>946920000</v>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>6.13%→6.35%</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>87→90</t>
-        </is>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="B18" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>2471560000</v>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>6.13%→7.11%</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>87→94</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>-947128000</v>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>2.29%→2.00%</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>76→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>테스</t>
         </is>
       </c>
-      <c r="H15" s="15" t="n">
+      <c r="H19" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I15" s="15" t="n">
-        <v>-898560000</v>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>6.65%→6.53%</t>
-        </is>
-      </c>
-      <c r="K15" s="13" t="inlineStr">
+      <c r="I19" s="15" t="n">
+        <v>-887328000</v>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>6.65%→6.18%</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
         <is>
           <t>201→195</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="17" t="n"/>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="17" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="17" t="n"/>
-      <c r="G16" s="14" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="17" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>-1365000000</v>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>3.45%→2.92%</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>55→50</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>대주전자재료</t>
         </is>
       </c>
-      <c r="H16" s="15" t="n">
+      <c r="H21" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I16" s="15" t="n">
-        <v>-453440000</v>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>0.66%→0.53%</t>
-        </is>
-      </c>
-      <c r="K16" s="13" t="inlineStr">
+      <c r="I21" s="15" t="n">
+        <v>-453960000</v>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>0.66%→0.51%</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
         <is>
           <t>31→26</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,820억   ·   현금 11억(0.3%)      주말 2026-08-21  vs  주초 2026-08-18      매수 1종목  /  매도 2종목</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n">
-        <v>424</v>
-      </c>
-      <c r="C21" s="11" t="n">
-        <v>3162573600</v>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.83%</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>0→424</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>-123</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>-1470514200</v>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>1.09%→0.69%</t>
-        </is>
-      </c>
-      <c r="K21" s="13" t="inlineStr">
-        <is>
-          <t>345→222</t>
         </is>
       </c>
     </row>
@@ -1264,622 +1324,1501 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>-477984000</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>4.49%→4.61%</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>184→180</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,820억   ·   현금 41억(1.0%)      주말 2026-08-21  vs  주초 2026-08-18      매수 7종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="8" t="n"/>
+      <c r="J25" s="8" t="n"/>
+      <c r="K25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>564</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>5468865480</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.37%</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>0→564</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>나이벡  (편출)</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>-527</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>-4739311000</v>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>1.18%→0.00%</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>527→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>에이프릴바이오</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>775646250</v>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>3.73%→3.01%</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>999→1,068</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>-155</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>-1889984750</v>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>1.09%→0.58%</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>345→190</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>796145000</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>2.62%→2.65%</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>613→663</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>-1077573000</v>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>9.37%→9.92%</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>226→220</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>한올바이오파마</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>794769600</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>5.20%→5.68%</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>659→683</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
           <t>녹십자</t>
         </is>
       </c>
-      <c r="H22" s="15" t="n">
+      <c r="H30" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I22" s="15" t="n">
-        <v>-320045000</v>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>3.12%→2.98%</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="inlineStr">
+      <c r="I30" s="15" t="n">
+        <v>-331683000</v>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>3.12%→2.96%</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
         <is>
           <t>183→178</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
-      <c r="E24" s="19" t="n"/>
-      <c r="F24" s="19" t="n"/>
-      <c r="G24" s="19" t="n"/>
-      <c r="H24" s="19" t="n"/>
-      <c r="I24" s="19" t="n"/>
-      <c r="J24" s="19" t="n"/>
-      <c r="K24" s="19" t="n"/>
-    </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="n"/>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="19" t="n"/>
-      <c r="E26" s="19" t="n"/>
-      <c r="F26" s="19" t="n"/>
-      <c r="G26" s="19" t="n"/>
-      <c r="H26" s="19" t="n"/>
-      <c r="I26" s="19" t="n"/>
-      <c r="J26" s="19" t="n"/>
-      <c r="K26" s="19" t="n"/>
-    </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억   ·   현금 2억(0.6%)      주말 2026-08-21  vs  주초 2026-08-18      매수 8종목  /  매도 5종목</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>코미코  (신규)</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>395</v>
+        <v>18</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1633088000</v>
+        <v>785565000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>0.00%→5.56%</t>
+          <t>8.85%→8.93%</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>0→395</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="n">
-        <v>-50</v>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>-145350000</v>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>8.32%→7.37%</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="inlineStr">
-        <is>
-          <t>795→745</t>
-        </is>
-      </c>
+          <t>797→815</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="n"/>
+      <c r="H31" s="17" t="n"/>
+      <c r="I31" s="17" t="n"/>
+      <c r="J31" s="17" t="n"/>
+      <c r="K31" s="17" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>코스맥스엔비티</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B32" s="11" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>41847120</v>
+        <v>752343800</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>0.27%→0.39%</t>
+          <t>7.99%→8.03%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>122→191</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>덕산하이메탈</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I32" s="15" t="n">
-        <v>-24858080</v>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>0.60%→0.48%</t>
-        </is>
-      </c>
-      <c r="K32" s="13" t="inlineStr">
-        <is>
-          <t>227→193</t>
-        </is>
-      </c>
+          <t>540→553</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="n"/>
+      <c r="H32" s="17" t="n"/>
+      <c r="I32" s="17" t="n"/>
+      <c r="J32" s="17" t="n"/>
+      <c r="K32" s="17" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>42332000</v>
+        <v>656224500</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>0.16%→0.29%</t>
+          <t>4.73%→5.11%</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>51→101</t>
-        </is>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>-14</v>
-      </c>
-      <c r="I33" s="15" t="n">
-        <v>-36176000</v>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>2.99%→2.70%</t>
-        </is>
-      </c>
-      <c r="K33" s="13" t="inlineStr">
-        <is>
-          <t>321→307</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>한선엔지니어링</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="C34" s="11" t="n">
-        <v>34186320</v>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>1.39%→1.43%</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>474→516</t>
-        </is>
-      </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>디앤디파마텍</t>
-        </is>
-      </c>
-      <c r="H34" s="15" t="n">
-        <v>-11</v>
-      </c>
-      <c r="I34" s="15" t="n">
-        <v>-48571600</v>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>0.48%→0.29%</t>
-        </is>
-      </c>
-      <c r="K34" s="13" t="inlineStr">
-        <is>
-          <t>30→19</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="C35" s="11" t="n">
-        <v>27481600</v>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>6.04%→5.81%</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>977→993</t>
-        </is>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>ISC</t>
-        </is>
-      </c>
-      <c r="H35" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I35" s="15" t="n">
-        <v>-40424400</v>
-      </c>
-      <c r="J35" s="16" t="inlineStr">
-        <is>
-          <t>1.99%→1.74%</t>
-        </is>
-      </c>
-      <c r="K35" s="13" t="inlineStr">
-        <is>
-          <t>41→38</t>
-        </is>
-      </c>
+          <t>90→93</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="n"/>
+      <c r="H33" s="17" t="n"/>
+      <c r="I33" s="17" t="n"/>
+      <c r="J33" s="17" t="n"/>
+      <c r="K33" s="17" t="n"/>
+    </row>
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,647억   ·   현금 80억(2.9%)      주말 2026-08-21  vs  주초 2026-08-18      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>스피어</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="C36" s="11" t="n">
-        <v>22891200</v>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>2.44%→2.38%</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>355→367</t>
-        </is>
-      </c>
-      <c r="G36" s="17" t="n"/>
-      <c r="H36" s="17" t="n"/>
-      <c r="I36" s="17" t="n"/>
-      <c r="J36" s="17" t="n"/>
-      <c r="K36" s="17" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>오름테라퓨틱  (신규)</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="C37" s="11" t="n">
-        <v>58770800</v>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.20%</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>0→11</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="n"/>
-      <c r="H37" s="17" t="n"/>
-      <c r="I37" s="17" t="n"/>
-      <c r="J37" s="17" t="n"/>
-      <c r="K37" s="17" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>비나텍</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" s="11" t="n">
-        <v>24472000</v>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>2.71%→2.65%</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>154→159</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="n"/>
-      <c r="H38" s="17" t="n"/>
-      <c r="I38" s="17" t="n"/>
-      <c r="J38" s="17" t="n"/>
-      <c r="K38" s="17" t="n"/>
-    </row>
-    <row r="40" ht="19" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억   ·   현금 8억(1.5%)      주말 2026-08-21  vs  주초 2026-08-18      매수 1종목  /  매도 1종목</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="n"/>
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,208억   ·   현금 60억(2.6%)      주말 2026-08-21  vs  주초 2026-08-18      매수 4종목  /  매도 9종목</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="K38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="8" t="n"/>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="8" t="n"/>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="8" t="n"/>
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>한올바이오파마</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>221</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>4703764000</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>1.75%→3.95%</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>200→421</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>고영  (편출)</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>-194</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>-2133806000</v>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>0.92%→0.00%</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>194→0</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H42" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J42" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K42" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>187</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>4558686000</v>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>1.51%→3.63%</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>151→338</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>-184</v>
+      </c>
+      <c r="I42" s="15" t="n">
+        <v>-6937904000</v>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>3.90%→1.10%</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>250→66</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>67</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>4421598000</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>13.34%→15.13%</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>453→520</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>-125</v>
+      </c>
+      <c r="I43" s="15" t="n">
+        <v>-4602750000</v>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>6.49%→4.29%</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>389→264</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>3284400000</v>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>2.63%→4.03%</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>100→156</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>케어젠  (편출)</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>-102</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>-2146692000</v>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>0.92%→0.00%</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>102→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="17" t="n"/>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>에임드바이오</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>-101</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>-908293000</v>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>0.81%→0.40%</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>203→102</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="n"/>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>지아이이노베이션</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>-80</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>-235824000</v>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>0.26%→0.15%</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>199→119</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="n"/>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n"/>
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="17" t="n"/>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>-67</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>-685678000</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>0.71%→0.37%</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>150→83</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="n"/>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>토모큐브</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>-41</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-429352000</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>0.54%→0.28%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>101→60</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="n"/>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>네이처셀</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-230724000</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>0.16%→0.06%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>46→17</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억   ·   현금 1억(0.3%)      주말 2026-08-21  vs  주초 2026-08-18      매수 8종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="8" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>코미코  (신규)</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>395</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>1633088000</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→5.56%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>0→395</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-145350000</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>8.32%→7.37%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>795→745</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>41847120</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>0.27%→0.39%</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>122→191</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-24858080</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>0.60%→0.48%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>227→193</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>노바렉스</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>42332000</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>0.16%→0.29%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>51→101</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>-36176000</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>2.99%→2.70%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>321→307</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>한선엔지니어링</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>34186320</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>1.39%→1.43%</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>474→516</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>-48571600</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>0.48%→0.29%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>30→19</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>27481600</v>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>6.04%→5.81%</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>977→993</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>-40424400</v>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>1.99%→1.74%</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>41→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>스피어</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>22891200</v>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>2.44%→2.38%</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>355→367</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="n"/>
+      <c r="H59" s="17" t="n"/>
+      <c r="I59" s="17" t="n"/>
+      <c r="J59" s="17" t="n"/>
+      <c r="K59" s="17" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱  (신규)</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>58770800</v>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.20%</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>0→11</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="n"/>
+      <c r="H60" s="17" t="n"/>
+      <c r="I60" s="17" t="n"/>
+      <c r="J60" s="17" t="n"/>
+      <c r="K60" s="17" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>24472000</v>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>2.71%→2.65%</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>154→159</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="n"/>
+      <c r="H61" s="17" t="n"/>
+      <c r="I61" s="17" t="n"/>
+      <c r="J61" s="17" t="n"/>
+      <c r="K61" s="17" t="n"/>
+    </row>
+    <row r="63" ht="19" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억   ·   현금 3억(0.4%)      주말 2026-08-21  vs  주초 2026-08-18      매수 4종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n"/>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="4" t="n"/>
+      <c r="H63" s="4" t="n"/>
+      <c r="I63" s="4" t="n"/>
+      <c r="J63" s="4" t="n"/>
+      <c r="K63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="8" t="n"/>
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="8" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
           <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
         </is>
       </c>
-      <c r="B43" s="11" t="n">
-        <v>655</v>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>1089789000</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→1.99%</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>0→655</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
+      <c r="B66" s="11" t="n">
+        <v>878</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>1899061320</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→3.32%</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>0→878</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
         <is>
           <t>한스바이오메드</t>
         </is>
       </c>
-      <c r="H43" s="15" t="n">
-        <v>-210</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>-472306800</v>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>2.66%→1.65%</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>612→402</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="H66" s="15" t="n">
+        <v>-301</v>
+      </c>
+      <c r="I66" s="15" t="n">
+        <v>-692601000</v>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>2.66%→1.25%</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>612→311</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>프로티나  (신규)</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>227</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>953581600</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.67%</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>0→227</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>에이프릴바이오</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="n">
+        <v>-230</v>
+      </c>
+      <c r="I67" s="15" t="n">
+        <v>-576725000</v>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>2.71%→1.02%</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>464→234</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>321774200</v>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>3.63%→4.34%</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>498→572</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>리브스메드</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="n">
+        <v>-116</v>
+      </c>
+      <c r="I68" s="15" t="n">
+        <v>-507824800</v>
+      </c>
+      <c r="J68" s="16" t="inlineStr">
+        <is>
+          <t>3.31%→1.78%</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>349→233</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>287896400</v>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>5.63%→6.35%</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>256→278</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>휴젤</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I69" s="15" t="n">
+        <v>-587640000</v>
+      </c>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>3.54%→2.41%</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>67→47</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="19" customHeight="1">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="19" t="n"/>
-      <c r="F45" s="19" t="n"/>
-      <c r="G45" s="19" t="n"/>
-      <c r="H45" s="19" t="n"/>
-      <c r="I45" s="19" t="n"/>
-      <c r="J45" s="19" t="n"/>
-      <c r="K45" s="19" t="n"/>
+      <c r="B71" s="20" t="n"/>
+      <c r="C71" s="20" t="n"/>
+      <c r="D71" s="20" t="n"/>
+      <c r="E71" s="20" t="n"/>
+      <c r="F71" s="20" t="n"/>
+      <c r="G71" s="20" t="n"/>
+      <c r="H71" s="20" t="n"/>
+      <c r="I71" s="20" t="n"/>
+      <c r="J71" s="20" t="n"/>
+      <c r="K71" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A29:E29"/>
+  <mergeCells count="20">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="G52:K52"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A71:K71"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="G64:K64"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="G29:K29"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="G41:K41"/>
-    <mergeCell ref="G19:K19"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="G25:K25"/>
+    <mergeCell ref="A63:K63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_weekly_20260821.xlsx
+++ b/reports/pdf_weekly_20260821.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,586억   ·   현금 82억(1.7%)      주말 2026-08-21  vs  주초 2026-08-18      매수 13종목  /  매도 17종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,658억   ·   현금 41억(0.9%)      주말 2026-08-21  vs  주초 2026-08-18      매수 13종목  /  매도 17종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>420</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>9522240000</v>
+        <v>9476460000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-283</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2866676800</v>
+        <v>-2852894700</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>149</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>7438080000</v>
+        <v>7402320000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-101</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1340310400</v>
+        <v>-1333866600</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>113</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>461853600</v>
+        <v>459633150</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-93</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1343440800</v>
+        <v>-1336981950</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>54</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1462968000</v>
+        <v>1455934500</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-79</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-3031704000</v>
+        <v>-3017128500</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>43</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>478951200</v>
+        <v>476648550</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-38</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1414816000</v>
+        <v>-1408014000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>36</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>449280000</v>
+        <v>447120000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-24</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-968448000</v>
+        <v>-963792000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>17</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>885768000</v>
+        <v>881509500</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-23</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-464048000</v>
+        <v>-461817000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1613040000</v>
+        <v>1605285000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-13</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-939640000</v>
+        <v>-935122500</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>536536000</v>
+        <v>533956500</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-305760000</v>
+        <v>-468234000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.10%</t>
+          <t>1.48%→1.35%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>31→19</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>506688000</v>
+        <v>504252000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1080,23 +1080,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-470496000</v>
+        <v>-304290000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.48%→1.35%</t>
+          <t>0.17%→0.10%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>31→19</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>939224000</v>
+        <v>934708500</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>-11</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-226283200</v>
+        <v>-225195300</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>9</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1038024000</v>
+        <v>1033033500</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>-8</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-324480000</v>
+        <v>-322920000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>7</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2471560000</v>
+        <v>2459677500</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>-7</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-947128000</v>
+        <v>-942574500</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>-6</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-887328000</v>
+        <v>-883062000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1268,23 +1268,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1365000000</v>
+        <v>-451777500</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>3.45%→2.92%</t>
+          <t>0.66%→0.51%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>31→26</t>
         </is>
       </c>
     </row>
@@ -1296,23 +1296,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-453960000</v>
+        <v>-1358437500</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.66%→0.51%</t>
+          <t>3.45%→2.92%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>31→26</t>
+          <t>55→50</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
         <v>-4</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-477984000</v>
+        <v>-475686000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,820억   ·   현금 41억(1.0%)      주말 2026-08-21  vs  주초 2026-08-18      매수 7종목  /  매도 4종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,981억   ·   현금 20억(0.5%)      주말 2026-08-21  vs  주초 2026-08-18      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1443,7 +1443,7 @@
         <v>564</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>5468865480</v>
+        <v>5458527360</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>-527</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-4739311000</v>
+        <v>-4730352000</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>69</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>775646250</v>
+        <v>774180000</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>-155</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1889984750</v>
+        <v>-1886412000</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>50</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>796145000</v>
+        <v>794640000</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>-6</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1077573000</v>
+        <v>-1075536000</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>794769600</v>
+        <v>793267200</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>-5</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-331683000</v>
+        <v>-331056000</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>18</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>785565000</v>
+        <v>784080000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>13</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>752343800</v>
+        <v>750921600</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>3</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>656224500</v>
+        <v>654984000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,647억   ·   현금 80억(2.9%)      주말 2026-08-21  vs  주초 2026-08-18      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,682억   ·   현금 40억(1.5%)      주말 2026-08-21  vs  주초 2026-08-18      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
@@ -1720,7 +1720,7 @@
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,208억   ·   현금 60억(2.6%)      주말 2026-08-21  vs  주초 2026-08-18      매수 4종목  /  매도 9종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,265억   ·   현금 30억(1.3%)      주말 2026-08-21  vs  주초 2026-08-18      매수 4종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>
@@ -1816,7 +1816,7 @@
         <v>221</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>4703764000</v>
+        <v>4662260200</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>-194</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-2133806000</v>
+        <v>-2114978300</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>187</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>4558686000</v>
+        <v>4518462300</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>-184</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-6937904000</v>
+        <v>-6876687200</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>67</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>4421598000</v>
+        <v>4382583900</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>-125</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-4602750000</v>
+        <v>-4562137500</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>56</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>3284400000</v>
+        <v>3255420000</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>-102</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-2146692000</v>
+        <v>-2127750600</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>-101</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-908293000</v>
+        <v>-900278650</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>-80</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-235824000</v>
+        <v>-233743200</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>-67</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-685678000</v>
+        <v>-679627900</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>-41</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-429352000</v>
+        <v>-425563600</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>-29</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-230724000</v>
+        <v>-228688200</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
     <row r="51" ht="19" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억   ·   현금 1억(0.3%)      주말 2026-08-21  vs  주초 2026-08-18      매수 8종목  /  매도 5종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 283억   ·   현금 1억(0.3%)      주말 2026-08-21  vs  주초 2026-08-18      매수 8종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B51" s="4" t="n"/>
@@ -2221,11 +2221,11 @@
         <v>395</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>1633088000</v>
+        <v>1590112000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>0.00%→5.56%</t>
+          <t>0.00%→5.45%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2242,11 +2242,11 @@
         <v>-50</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-145350000</v>
+        <v>-143560000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>8.32%→7.37%</t>
+          <t>8.27%→7.33%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2265,11 +2265,11 @@
         <v>69</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>41847120</v>
+        <v>41869200</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>0.27%→0.39%</t>
+          <t>0.27%→0.40%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -2286,11 +2286,11 @@
         <v>-34</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-24858080</v>
+        <v>-24505840</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.48%</t>
+          <t>0.59%→0.48%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2309,11 +2309,11 @@
         <v>50</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>42332000</v>
+        <v>41403000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>0.16%→0.29%</t>
+          <t>0.15%→0.29%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2330,11 +2330,11 @@
         <v>-14</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-36176000</v>
+        <v>-36933400</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>2.99%→2.70%</t>
+          <t>3.07%→2.78%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2353,11 +2353,11 @@
         <v>42</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>34186320</v>
+        <v>33690720</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>1.39%→1.43%</t>
+          <t>1.38%→1.42%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2374,11 +2374,11 @@
         <v>-11</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-48571600</v>
+        <v>-47049200</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.29%</t>
+          <t>0.46%→0.28%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2397,7 +2397,7 @@
         <v>16</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>27481600</v>
+        <v>27291200</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
@@ -2418,11 +2418,11 @@
         <v>-3</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-40424400</v>
+        <v>-37451400</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>1.99%→1.74%</t>
+          <t>1.85%→1.63%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2441,11 +2441,11 @@
         <v>12</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>22891200</v>
+        <v>22866000</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>2.44%→2.38%</t>
+          <t>2.45%→2.40%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -2469,7 +2469,7 @@
         <v>11</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>58770800</v>
+        <v>58363800</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
@@ -2497,11 +2497,11 @@
         <v>5</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>24472000</v>
+        <v>24827000</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>2.71%→2.65%</t>
+          <t>2.77%→2.71%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2518,7 +2518,7 @@
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억   ·   현금 3억(0.4%)      주말 2026-08-21  vs  주초 2026-08-18      매수 4종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 570억   ·   현금 3억(0.4%)      주말 2026-08-21  vs  주초 2026-08-18      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B63" s="4" t="n"/>
@@ -2614,7 +2614,7 @@
         <v>878</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>1899061320</v>
+        <v>1915155060</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>-301</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-692601000</v>
+        <v>-698470500</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>227</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>953581600</v>
+        <v>961662800</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>-230</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-576725000</v>
+        <v>-581612500</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>74</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>321774200</v>
+        <v>324501100</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>-116</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-507824800</v>
+        <v>-512128400</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>22</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>287896400</v>
+        <v>290336200</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>-20</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-587640000</v>
+        <v>-592620000</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_weekly_20260821.xlsx
+++ b/reports/pdf_weekly_20260821.xlsx
@@ -1268,23 +1268,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-451777500</v>
+        <v>-1358437500</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.66%→0.51%</t>
+          <t>3.45%→2.92%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>31→26</t>
+          <t>55→50</t>
         </is>
       </c>
     </row>
@@ -1296,23 +1296,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1358437500</v>
+        <v>-451777500</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>3.45%→2.92%</t>
+          <t>0.66%→0.51%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>31→26</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20260821.xlsx
+++ b/reports/pdf_weekly_20260821.xlsx
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-468234000</v>
+        <v>-304290000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.48%→1.35%</t>
+          <t>0.17%→0.10%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>31→19</t>
         </is>
       </c>
     </row>
@@ -1080,23 +1080,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-304290000</v>
+        <v>-468234000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.10%</t>
+          <t>1.48%→1.35%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>31→19</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
@@ -1268,23 +1268,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1358437500</v>
+        <v>-451777500</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>3.45%→2.92%</t>
+          <t>0.66%→0.51%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>31→26</t>
         </is>
       </c>
     </row>
@@ -1296,23 +1296,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-451777500</v>
+        <v>-1358437500</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.66%→0.51%</t>
+          <t>3.45%→2.92%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>31→26</t>
+          <t>55→50</t>
         </is>
       </c>
     </row>
